--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_o_higgins.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_o_higgins.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>30.03978860038458</v>
+      </c>
+      <c r="C2">
         <v>25.40786338844075</v>
-      </c>
-      <c r="C2">
-        <v>30.03978860038458</v>
       </c>
       <c r="D2">
         <v>3.935789423580371</v>
       </c>
       <c r="E2">
-        <v>16.34496440658187</v>
+        <v>19.32469755319563</v>
       </c>
       <c r="F2">
         <v>64.33033804022251</v>
       </c>
       <c r="G2">
-        <v>19.32469755319563</v>
+        <v>16.34496440658187</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.83882783882784</v>
+      </c>
+      <c r="C3">
         <v>25.43012543012543</v>
-      </c>
-      <c r="C3">
-        <v>27.83882783882784</v>
       </c>
       <c r="D3">
         <v>3.932343954604976</v>
       </c>
       <c r="E3">
-        <v>16.59183082271147</v>
+        <v>18.16338354577056</v>
       </c>
       <c r="F3">
         <v>65.24478563151796</v>
       </c>
       <c r="G3">
-        <v>18.16338354577056</v>
+        <v>16.59183082271147</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.26668134772077</v>
+      </c>
+      <c r="C4">
         <v>33.64897599647655</v>
-      </c>
-      <c r="C4">
-        <v>29.26668134772077</v>
       </c>
       <c r="D4">
         <v>2.971858638743456</v>
       </c>
       <c r="E4">
-        <v>20.65423087320897</v>
+        <v>17.96431467964315</v>
       </c>
       <c r="F4">
-        <v>61.38145444714787</v>
+        <v>61.38145444714788</v>
       </c>
       <c r="G4">
-        <v>17.96431467964315</v>
+        <v>20.65423087320898</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.90754183540918</v>
+      </c>
+      <c r="C5">
         <v>30.04508290670131</v>
-      </c>
-      <c r="C5">
-        <v>29.90754183540918</v>
       </c>
       <c r="D5">
         <v>3.328331637843337</v>
       </c>
       <c r="E5">
-        <v>18.78373859456361</v>
+        <v>18.6977499641714</v>
       </c>
       <c r="F5">
         <v>62.51851144126499</v>
       </c>
       <c r="G5">
-        <v>18.6977499641714</v>
+        <v>18.78373859456361</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.06924882629108</v>
+      </c>
+      <c r="C6">
         <v>27.62617370892019</v>
-      </c>
-      <c r="C6">
-        <v>33.06924882629108</v>
       </c>
       <c r="D6">
         <v>3.61975570897504</v>
       </c>
       <c r="E6">
-        <v>17.19163699443075</v>
+        <v>20.57883684835205</v>
       </c>
       <c r="F6">
         <v>62.2295261572172</v>
       </c>
       <c r="G6">
-        <v>20.57883684835205</v>
+        <v>17.19163699443075</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.24343443275268</v>
+      </c>
+      <c r="C7">
         <v>23.08338491466973</v>
-      </c>
-      <c r="C7">
-        <v>33.24343443275268</v>
       </c>
       <c r="D7">
         <v>4.3321202834706</v>
       </c>
       <c r="E7">
-        <v>14.76610668024209</v>
+        <v>21.26534306239041</v>
       </c>
       <c r="F7">
-        <v>63.96855025736749</v>
+        <v>63.9685502573675</v>
       </c>
       <c r="G7">
-        <v>21.26534306239041</v>
+        <v>14.7661066802421</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.7982922905581</v>
+      </c>
+      <c r="C8">
         <v>28.91350080435589</v>
-      </c>
-      <c r="C8">
-        <v>29.7982922905581</v>
       </c>
       <c r="D8">
         <v>3.458591910977959</v>
       </c>
       <c r="E8">
-        <v>18.21761334840747</v>
+        <v>18.77509648746637</v>
       </c>
       <c r="F8">
         <v>63.00729016412616</v>
       </c>
       <c r="G8">
-        <v>18.77509648746637</v>
+        <v>18.21761334840747</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>37.84511576080228</v>
+      </c>
+      <c r="C9">
         <v>20.43147208121827</v>
-      </c>
-      <c r="C9">
-        <v>37.84511576080228</v>
       </c>
       <c r="D9">
         <v>4.894409937888199</v>
       </c>
       <c r="E9">
-        <v>12.9087140175219</v>
+        <v>23.9107478097622</v>
       </c>
       <c r="F9">
         <v>63.1805381727159</v>
       </c>
       <c r="G9">
-        <v>23.9107478097622</v>
+        <v>12.9087140175219</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.07206012378426</v>
+      </c>
+      <c r="C10">
         <v>30.42661361626879</v>
-      </c>
-      <c r="C10">
-        <v>26.07206012378426</v>
       </c>
       <c r="D10">
         <v>3.286596440247003</v>
       </c>
       <c r="E10">
-        <v>19.44209039548022</v>
+        <v>16.65960451977401</v>
       </c>
       <c r="F10">
         <v>63.89830508474576</v>
       </c>
       <c r="G10">
-        <v>16.65960451977401</v>
+        <v>19.44209039548022</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.41020679646874</v>
+      </c>
+      <c r="C11">
         <v>26.16398597170154</v>
-      </c>
-      <c r="C11">
-        <v>32.41020679646874</v>
       </c>
       <c r="D11">
         <v>3.822047608042524</v>
       </c>
       <c r="E11">
-        <v>16.49952335557674</v>
+        <v>20.43851286939942</v>
       </c>
       <c r="F11">
         <v>63.06196377502383</v>
       </c>
       <c r="G11">
-        <v>20.43851286939942</v>
+        <v>16.49952335557674</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.96793099635077</v>
+      </c>
+      <c r="C12">
         <v>26.35187437797191</v>
-      </c>
-      <c r="C12">
-        <v>29.96793099635077</v>
       </c>
       <c r="D12">
         <v>3.794796475031473</v>
       </c>
       <c r="E12">
-        <v>16.85766836445954</v>
+        <v>19.17091114883984</v>
       </c>
       <c r="F12">
         <v>63.97142048670063</v>
       </c>
       <c r="G12">
-        <v>19.17091114883984</v>
+        <v>16.85766836445954</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.10894446799491</v>
+      </c>
+      <c r="C13">
         <v>28.92115303094532</v>
-      </c>
-      <c r="C13">
-        <v>27.10894446799491</v>
       </c>
       <c r="D13">
         <v>3.457676804690363</v>
       </c>
       <c r="E13">
+        <v>17.37417645860219</v>
+      </c>
+      <c r="F13">
+        <v>64.09019900835428</v>
+      </c>
+      <c r="G13">
         <v>18.53562453304354</v>
-      </c>
-      <c r="F13">
-        <v>64.09019900835426</v>
-      </c>
-      <c r="G13">
-        <v>17.37417645860218</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.20205177526649</v>
+      </c>
+      <c r="C14">
         <v>31.74641340065721</v>
-      </c>
-      <c r="C14">
-        <v>27.20205177526649</v>
       </c>
       <c r="D14">
         <v>3.149962130775057</v>
       </c>
       <c r="E14">
-        <v>19.97277127874143</v>
+        <v>17.11375554659137</v>
       </c>
       <c r="F14">
         <v>62.9134731746672</v>
       </c>
       <c r="G14">
-        <v>17.11375554659137</v>
+        <v>19.97277127874143</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.55687643145381</v>
+      </c>
+      <c r="C15">
         <v>28.12738575635293</v>
-      </c>
-      <c r="C15">
-        <v>26.55687643145381</v>
       </c>
       <c r="D15">
         <v>3.555253974408686</v>
       </c>
       <c r="E15">
-        <v>18.1837410984982</v>
+        <v>17.16844109144751</v>
       </c>
       <c r="F15">
         <v>64.64781781005429</v>
       </c>
       <c r="G15">
-        <v>17.16844109144751</v>
+        <v>18.1837410984982</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.48212309197148</v>
+      </c>
+      <c r="C16">
         <v>26.06244690983037</v>
-      </c>
-      <c r="C16">
-        <v>30.48212309197148</v>
       </c>
       <c r="D16">
         <v>3.836938271604938</v>
       </c>
       <c r="E16">
-        <v>16.64857932123126</v>
+        <v>19.47184951328598</v>
       </c>
       <c r="F16">
         <v>63.87957116548277</v>
       </c>
       <c r="G16">
-        <v>19.47184951328598</v>
+        <v>16.64857932123126</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>29.25509993818257</v>
+      </c>
+      <c r="C17">
         <v>22.76426952400577</v>
-      </c>
-      <c r="C17">
-        <v>29.25509993818257</v>
       </c>
       <c r="D17">
         <v>4.392849060873501</v>
       </c>
       <c r="E17">
+        <v>19.24432395798034</v>
+      </c>
+      <c r="F17">
+        <v>65.78109115554048</v>
+      </c>
+      <c r="G17">
         <v>14.97458488647916</v>
-      </c>
-      <c r="F17">
-        <v>65.78109115554049</v>
-      </c>
-      <c r="G17">
-        <v>19.24432395798035</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>30.1630713479881</v>
+      </c>
+      <c r="C18">
         <v>30.90150764076442</v>
-      </c>
-      <c r="C18">
-        <v>30.1630713479881</v>
       </c>
       <c r="D18">
         <v>3.23608806283881</v>
       </c>
       <c r="E18">
-        <v>19.18578736229915</v>
+        <v>18.72731517840086</v>
       </c>
       <c r="F18">
         <v>62.08689745929998</v>
       </c>
       <c r="G18">
-        <v>18.72731517840086</v>
+        <v>19.18578736229915</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>25.71196754563895</v>
+      </c>
+      <c r="C19">
         <v>27.09939148073022</v>
-      </c>
-      <c r="C19">
-        <v>25.71196754563895</v>
       </c>
       <c r="D19">
         <v>3.690119760479042</v>
       </c>
       <c r="E19">
-        <v>17.73388552617607</v>
+        <v>16.82595306360837</v>
       </c>
       <c r="F19">
         <v>65.44016141021557</v>
       </c>
       <c r="G19">
-        <v>16.82595306360837</v>
+        <v>17.73388552617607</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.22415669205658</v>
+      </c>
+      <c r="C20">
         <v>42.05658324265506</v>
-      </c>
-      <c r="C20">
-        <v>26.22415669205658</v>
       </c>
       <c r="D20">
         <v>2.377749029754205</v>
       </c>
       <c r="E20">
-        <v>24.9919172324604</v>
+        <v>15.58357581635952</v>
       </c>
       <c r="F20">
-        <v>59.42450695118009</v>
+        <v>59.42450695118008</v>
       </c>
       <c r="G20">
-        <v>15.58357581635952</v>
+        <v>24.99191723246039</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.26627218934911</v>
+      </c>
+      <c r="C21">
         <v>33.68047337278107</v>
-      </c>
-      <c r="C21">
-        <v>27.26627218934911</v>
       </c>
       <c r="D21">
         <v>2.969079409697822</v>
       </c>
       <c r="E21">
-        <v>20.92647058823529</v>
+        <v>16.94117647058824</v>
       </c>
       <c r="F21">
-        <v>62.13235294117646</v>
+        <v>62.13235294117648</v>
       </c>
       <c r="G21">
-        <v>16.94117647058823</v>
+        <v>20.9264705882353</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>22.64150943396227</v>
+      </c>
+      <c r="C22">
         <v>32.76857912976511</v>
-      </c>
-      <c r="C22">
-        <v>22.64150943396227</v>
       </c>
       <c r="D22">
         <v>3.051703877790835</v>
       </c>
       <c r="E22">
+        <v>14.56888007928642</v>
+      </c>
+      <c r="F22">
+        <v>64.34588701684837</v>
+      </c>
+      <c r="G22">
         <v>21.08523290386522</v>
-      </c>
-      <c r="F22">
-        <v>64.34588701684838</v>
-      </c>
-      <c r="G22">
-        <v>14.56888007928642</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.82611258473327</v>
+      </c>
+      <c r="C23">
         <v>49.7789566755084</v>
-      </c>
-      <c r="C23">
-        <v>29.82611258473327</v>
       </c>
       <c r="D23">
         <v>2.008880994671403</v>
       </c>
       <c r="E23">
-        <v>27.71578601903512</v>
+        <v>16.60649819494585</v>
       </c>
       <c r="F23">
         <v>55.67771578601904</v>
       </c>
       <c r="G23">
-        <v>16.60649819494585</v>
+        <v>27.71578601903512</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>22.84701114488348</v>
+      </c>
+      <c r="C24">
         <v>40.52684903748733</v>
-      </c>
-      <c r="C24">
-        <v>22.84701114488348</v>
       </c>
       <c r="D24">
         <v>2.4675</v>
       </c>
       <c r="E24">
-        <v>24.8062015503876</v>
+        <v>13.98449612403101</v>
       </c>
       <c r="F24">
         <v>61.2093023255814</v>
       </c>
       <c r="G24">
-        <v>13.98449612403101</v>
+        <v>24.8062015503876</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.90753983441774</v>
+      </c>
+      <c r="C25">
         <v>26.20913321112745</v>
-      </c>
-      <c r="C25">
-        <v>29.90753983441774</v>
       </c>
       <c r="D25">
         <v>3.815463838290677</v>
       </c>
       <c r="E25">
-        <v>16.78817047521968</v>
+        <v>19.15717216552044</v>
       </c>
       <c r="F25">
         <v>64.05465735925988</v>
       </c>
       <c r="G25">
-        <v>19.15717216552044</v>
+        <v>16.78817047521967</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>31.32623641605677</v>
+      </c>
+      <c r="C26">
         <v>33.93213572854291</v>
-      </c>
-      <c r="C26">
-        <v>31.32623641605677</v>
       </c>
       <c r="D26">
         <v>2.947058823529412</v>
       </c>
       <c r="E26">
-        <v>20.53277863517413</v>
+        <v>18.95591491645978</v>
       </c>
       <c r="F26">
         <v>60.51130644836611</v>
       </c>
       <c r="G26">
-        <v>18.95591491645978</v>
+        <v>20.53277863517413</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.83091290750975</v>
+      </c>
+      <c r="C27">
         <v>27.05307801053849</v>
-      </c>
-      <c r="C27">
-        <v>28.83091290750975</v>
       </c>
       <c r="D27">
         <v>3.696437054631829</v>
       </c>
       <c r="E27">
-        <v>17.35462240299</v>
+        <v>18.49510827745411</v>
       </c>
       <c r="F27">
         <v>64.1502693195559</v>
       </c>
       <c r="G27">
-        <v>18.49510827745411</v>
+        <v>17.35462240299</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.03791469194313</v>
+      </c>
+      <c r="C28">
         <v>37.32227488151658</v>
-      </c>
-      <c r="C28">
-        <v>27.03791469194313</v>
       </c>
       <c r="D28">
         <v>2.679365079365079</v>
       </c>
       <c r="E28">
-        <v>22.7076124567474</v>
+        <v>16.45040369088812</v>
       </c>
       <c r="F28">
         <v>60.84198385236448</v>
       </c>
       <c r="G28">
-        <v>16.45040369088812</v>
+        <v>22.7076124567474</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.97896891866741</v>
+      </c>
+      <c r="C29">
         <v>29.9181090638377</v>
-      </c>
-      <c r="C29">
-        <v>30.97896891866741</v>
       </c>
       <c r="D29">
         <v>3.342457231726283</v>
       </c>
       <c r="E29">
-        <v>18.59456333140544</v>
+        <v>19.2539039907461</v>
       </c>
       <c r="F29">
         <v>62.15153267784846</v>
       </c>
       <c r="G29">
-        <v>19.2539039907461</v>
+        <v>18.59456333140544</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.34158288218613</v>
+      </c>
+      <c r="C30">
         <v>29.59525650940964</v>
-      </c>
-      <c r="C30">
-        <v>25.34158288218613</v>
       </c>
       <c r="D30">
         <v>3.378919860627178</v>
       </c>
       <c r="E30">
+        <v>16.35607321131447</v>
+      </c>
+      <c r="F30">
+        <v>64.54242928452578</v>
+      </c>
+      <c r="G30">
         <v>19.10149750415973</v>
-      </c>
-      <c r="F30">
-        <v>64.5424292845258</v>
-      </c>
-      <c r="G30">
-        <v>16.35607321131448</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>26.80058147218184</v>
+      </c>
+      <c r="C31">
         <v>30.77837980705696</v>
-      </c>
-      <c r="C31">
-        <v>26.80058147218184</v>
       </c>
       <c r="D31">
         <v>3.249033920137398</v>
       </c>
       <c r="E31">
-        <v>19.53203622945321</v>
+        <v>17.00771553170077</v>
       </c>
       <c r="F31">
         <v>63.46024823884603</v>
       </c>
       <c r="G31">
-        <v>17.00771553170077</v>
+        <v>19.53203622945321</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.87483176312248</v>
+      </c>
+      <c r="C32">
         <v>28.4656796769852</v>
-      </c>
-      <c r="C32">
-        <v>25.87483176312248</v>
       </c>
       <c r="D32">
         <v>3.513002364066194</v>
       </c>
       <c r="E32">
-        <v>18.4434270765206</v>
+        <v>16.76477000218008</v>
       </c>
       <c r="F32">
         <v>64.79180292129932</v>
       </c>
       <c r="G32">
-        <v>16.76477000218008</v>
+        <v>18.4434270765206</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>23.5009671179884</v>
+      </c>
+      <c r="C33">
         <v>43.61702127659575</v>
-      </c>
-      <c r="C33">
-        <v>23.5009671179884</v>
       </c>
       <c r="D33">
         <v>2.292682926829268</v>
       </c>
       <c r="E33">
-        <v>26.09953703703704</v>
+        <v>14.0625</v>
       </c>
       <c r="F33">
         <v>59.83796296296297</v>
       </c>
       <c r="G33">
-        <v>14.0625</v>
+        <v>26.09953703703704</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.62118219115636</v>
+      </c>
+      <c r="C34">
         <v>27.58699285822823</v>
-      </c>
-      <c r="C34">
-        <v>27.62118219115636</v>
       </c>
       <c r="D34">
         <v>3.624896722665932</v>
       </c>
       <c r="E34">
-        <v>17.77418802163644</v>
+        <v>17.79621607068556</v>
       </c>
       <c r="F34">
         <v>64.42959590767801</v>
       </c>
       <c r="G34">
-        <v>17.79621607068556</v>
+        <v>17.77418802163644</v>
       </c>
     </row>
   </sheetData>
